--- a/v2/e2e/fixtures/test-transactions-bank-norwegian.xlsx
+++ b/v2/e2e/fixtures/test-transactions-bank-norwegian.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
   <si>
     <t>TransactionDate</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Pending at ZARA</t>
+  </si>
+  <si>
+    <t>Reservert</t>
+  </si>
+  <si>
+    <t>Clothing Stores, MEN, WOMEN, and CHIL</t>
   </si>
 </sst>
 </file>
@@ -474,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -685,6 +694,32 @@
       </c>
       <c r="K6" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>-299</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>-299</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
